--- a/data/samples/external/nhsa/H-UDMP-SAMPLE-NHSA-TRANSCODE-v1.0.xlsx
+++ b/data/samples/external/nhsa/H-UDMP-SAMPLE-NHSA-TRANSCODE-v1.0.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C07020813700004165590000001</t>
+          <t>C09100100000000211790000049</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C07020813700002165590000001</t>
+          <t>C09100100000000211790000050</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
